--- a/data/heart_disease_clean.xlsx
+++ b/data/heart_disease_clean.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>heart_disease_presence</t>
+          <t>severity_label</t>
         </is>
       </c>
     </row>
@@ -550,8 +550,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N2" t="n">
-        <v>0</v>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -604,8 +606,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N3" t="n">
-        <v>2</v>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -658,8 +662,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N4" t="n">
-        <v>1</v>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -712,8 +718,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -766,8 +774,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N6" t="n">
-        <v>0</v>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -820,8 +830,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N7" t="n">
-        <v>0</v>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -874,8 +886,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N8" t="n">
-        <v>3</v>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -928,8 +942,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -982,8 +998,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N10" t="n">
-        <v>2</v>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1036,8 +1054,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N11" t="n">
-        <v>1</v>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1090,8 +1110,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N12" t="n">
-        <v>0</v>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1144,8 +1166,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N13" t="n">
-        <v>0</v>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1198,8 +1222,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N14" t="n">
-        <v>2</v>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1252,8 +1278,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N15" t="n">
-        <v>0</v>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1306,8 +1334,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1360,8 +1390,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N17" t="n">
-        <v>0</v>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1414,8 +1446,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N18" t="n">
-        <v>1</v>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1468,8 +1502,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N19" t="n">
-        <v>0</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1522,8 +1558,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N20" t="n">
-        <v>0</v>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1576,8 +1614,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1630,8 +1670,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N22" t="n">
-        <v>0</v>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1684,8 +1726,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N23" t="n">
-        <v>0</v>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -1738,8 +1782,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N24" t="n">
-        <v>1</v>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -1792,8 +1838,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N25" t="n">
-        <v>3</v>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -1846,8 +1894,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N26" t="n">
-        <v>4</v>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -1900,8 +1950,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N27" t="n">
-        <v>0</v>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1954,8 +2006,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N28" t="n">
-        <v>0</v>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -2008,8 +2062,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N29" t="n">
-        <v>0</v>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -2062,8 +2118,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N30" t="n">
-        <v>0</v>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2116,8 +2174,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N31" t="n">
-        <v>3</v>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="32">
@@ -2170,8 +2230,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N32" t="n">
-        <v>0</v>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -2224,8 +2286,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N33" t="n">
-        <v>2</v>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="34">
@@ -2278,8 +2342,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N34" t="n">
-        <v>1</v>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2332,8 +2398,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N35" t="n">
-        <v>0</v>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="36">
@@ -2386,8 +2454,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N36" t="n">
-        <v>0</v>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -2440,8 +2510,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N37" t="n">
-        <v>0</v>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -2494,8 +2566,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N38" t="n">
-        <v>3</v>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -2548,8 +2622,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N39" t="n">
-        <v>1</v>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -2602,8 +2678,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N40" t="n">
-        <v>3</v>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="41">
@@ -2656,8 +2734,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N41" t="n">
-        <v>0</v>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -2710,8 +2790,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N42" t="n">
-        <v>4</v>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -2764,8 +2846,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N43" t="n">
-        <v>0</v>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -2818,8 +2902,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N44" t="n">
-        <v>0</v>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -2872,8 +2958,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N45" t="n">
-        <v>0</v>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -2926,8 +3014,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N46" t="n">
-        <v>1</v>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -2980,8 +3070,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N47" t="n">
-        <v>4</v>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -3034,8 +3126,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N48" t="n">
-        <v>0</v>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -3088,8 +3182,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N49" t="n">
-        <v>4</v>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3142,8 +3238,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N50" t="n">
-        <v>0</v>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3196,8 +3294,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N51" t="n">
-        <v>0</v>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -3250,8 +3350,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N52" t="n">
-        <v>0</v>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -3304,8 +3406,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N53" t="n">
-        <v>0</v>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="54">
@@ -3358,8 +3462,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N54" t="n">
-        <v>2</v>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -3412,8 +3518,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N55" t="n">
-        <v>0</v>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -3466,8 +3574,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N56" t="n">
-        <v>1</v>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -3520,8 +3630,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N57" t="n">
-        <v>1</v>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="58">
@@ -3574,8 +3686,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N58" t="n">
-        <v>1</v>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="59">
@@ -3628,8 +3742,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N59" t="n">
-        <v>1</v>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="60">
@@ -3682,8 +3798,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N60" t="n">
-        <v>0</v>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -3736,8 +3854,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N61" t="n">
-        <v>0</v>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="62">
@@ -3790,8 +3910,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N62" t="n">
-        <v>2</v>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="63">
@@ -3844,8 +3966,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N63" t="n">
-        <v>0</v>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -3898,8 +4022,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N64" t="n">
-        <v>1</v>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="65">
@@ -3952,8 +4078,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N65" t="n">
-        <v>0</v>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -4006,8 +4134,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N66" t="n">
-        <v>2</v>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -4060,8 +4190,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N67" t="n">
-        <v>2</v>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="68">
@@ -4114,8 +4246,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N68" t="n">
-        <v>1</v>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -4168,8 +4302,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N69" t="n">
-        <v>0</v>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="70">
@@ -4222,8 +4358,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N70" t="n">
-        <v>2</v>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="71">
@@ -4276,8 +4414,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N71" t="n">
-        <v>1</v>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="72">
@@ -4330,8 +4470,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N72" t="n">
-        <v>0</v>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="73">
@@ -4384,8 +4526,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N73" t="n">
-        <v>3</v>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="74">
@@ -4438,8 +4582,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N74" t="n">
-        <v>1</v>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -4492,8 +4638,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N75" t="n">
-        <v>1</v>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="76">
@@ -4546,8 +4694,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N76" t="n">
-        <v>1</v>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="77">
@@ -4600,8 +4750,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N77" t="n">
-        <v>0</v>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -4654,8 +4806,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N78" t="n">
-        <v>1</v>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="79">
@@ -4708,8 +4862,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N79" t="n">
-        <v>0</v>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -4762,8 +4918,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N80" t="n">
-        <v>0</v>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="81">
@@ -4816,8 +4974,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N81" t="n">
-        <v>3</v>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -4870,8 +5030,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N82" t="n">
-        <v>0</v>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="83">
@@ -4924,8 +5086,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N83" t="n">
-        <v>0</v>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -4978,8 +5142,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N84" t="n">
-        <v>0</v>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -5032,8 +5198,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N85" t="n">
-        <v>3</v>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="86">
@@ -5086,8 +5254,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N86" t="n">
-        <v>0</v>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="87">
@@ -5140,8 +5310,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N87" t="n">
-        <v>0</v>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="88">
@@ -5194,8 +5366,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N88" t="n">
-        <v>0</v>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="89">
@@ -5248,8 +5422,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N89" t="n">
-        <v>0</v>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="90">
@@ -5302,8 +5478,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N90" t="n">
-        <v>0</v>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5356,8 +5534,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N91" t="n">
-        <v>0</v>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -5410,8 +5590,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N92" t="n">
-        <v>3</v>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="93">
@@ -5464,8 +5646,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N93" t="n">
-        <v>0</v>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="94">
@@ -5518,8 +5702,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N94" t="n">
-        <v>0</v>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="95">
@@ -5572,8 +5758,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N95" t="n">
-        <v>0</v>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="96">
@@ -5626,8 +5814,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N96" t="n">
-        <v>1</v>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="97">
@@ -5680,8 +5870,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N97" t="n">
-        <v>2</v>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -5734,8 +5926,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N98" t="n">
-        <v>3</v>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="99">
@@ -5788,8 +5982,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N99" t="n">
-        <v>0</v>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -5842,8 +6038,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N100" t="n">
-        <v>0</v>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="101">
@@ -5896,8 +6094,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N101" t="n">
-        <v>0</v>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -5950,8 +6150,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N102" t="n">
-        <v>0</v>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="103">
@@ -6004,8 +6206,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N103" t="n">
-        <v>0</v>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="104">
@@ -6058,8 +6262,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N104" t="n">
-        <v>0</v>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="105">
@@ -6112,8 +6318,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N105" t="n">
-        <v>3</v>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="106">
@@ -6166,8 +6374,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N106" t="n">
-        <v>0</v>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -6220,8 +6430,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N107" t="n">
-        <v>2</v>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="108">
@@ -6274,8 +6486,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N108" t="n">
-        <v>1</v>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="109">
@@ -6328,8 +6542,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N109" t="n">
-        <v>2</v>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="110">
@@ -6382,8 +6598,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N110" t="n">
-        <v>3</v>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="111">
@@ -6436,8 +6654,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N111" t="n">
-        <v>1</v>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -6490,8 +6710,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N112" t="n">
-        <v>1</v>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -6544,8 +6766,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N113" t="n">
-        <v>0</v>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -6598,8 +6822,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N114" t="n">
-        <v>2</v>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -6652,8 +6878,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N115" t="n">
-        <v>2</v>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -6706,8 +6934,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N116" t="n">
-        <v>0</v>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -6760,8 +6990,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N117" t="n">
-        <v>0</v>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -6814,8 +7046,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N118" t="n">
-        <v>0</v>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -6868,8 +7102,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N119" t="n">
-        <v>3</v>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -6922,8 +7158,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N120" t="n">
-        <v>2</v>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -6976,8 +7214,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N121" t="n">
-        <v>3</v>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -7030,8 +7270,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N122" t="n">
-        <v>4</v>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -7084,8 +7326,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N123" t="n">
-        <v>0</v>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -7138,8 +7382,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N124" t="n">
-        <v>3</v>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -7192,8 +7438,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N125" t="n">
-        <v>1</v>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -7246,8 +7494,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N126" t="n">
-        <v>0</v>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -7300,8 +7550,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N127" t="n">
-        <v>3</v>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -7354,8 +7606,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N128" t="n">
-        <v>3</v>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -7408,8 +7662,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N129" t="n">
-        <v>0</v>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -7462,8 +7718,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N130" t="n">
-        <v>0</v>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="131">
@@ -7516,8 +7774,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N131" t="n">
-        <v>0</v>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="132">
@@ -7570,8 +7830,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N132" t="n">
-        <v>0</v>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="133">
@@ -7624,8 +7886,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N133" t="n">
-        <v>0</v>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="134">
@@ -7678,8 +7942,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N134" t="n">
-        <v>0</v>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="135">
@@ -7732,8 +7998,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N135" t="n">
-        <v>0</v>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="136">
@@ -7786,8 +8054,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N136" t="n">
-        <v>0</v>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="137">
@@ -7840,8 +8110,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N137" t="n">
-        <v>4</v>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="138">
@@ -7894,8 +8166,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N138" t="n">
-        <v>3</v>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="139">
@@ -7948,8 +8222,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N139" t="n">
-        <v>1</v>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="140">
@@ -8002,8 +8278,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N140" t="n">
-        <v>0</v>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -8056,8 +8334,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N141" t="n">
-        <v>0</v>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -8110,8 +8390,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N142" t="n">
-        <v>1</v>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="143">
@@ -8164,8 +8446,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N143" t="n">
-        <v>0</v>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="144">
@@ -8218,8 +8502,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N144" t="n">
-        <v>1</v>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="145">
@@ -8272,8 +8558,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N145" t="n">
-        <v>0</v>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="146">
@@ -8326,8 +8614,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N146" t="n">
-        <v>1</v>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="147">
@@ -8380,8 +8670,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N147" t="n">
-        <v>4</v>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="148">
@@ -8434,8 +8726,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N148" t="n">
-        <v>0</v>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -8488,8 +8782,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N149" t="n">
-        <v>0</v>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="150">
@@ -8542,8 +8838,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N150" t="n">
-        <v>0</v>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -8596,8 +8894,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N151" t="n">
-        <v>0</v>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="152">
@@ -8650,8 +8950,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N152" t="n">
-        <v>0</v>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="153">
@@ -8704,8 +9006,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N153" t="n">
-        <v>0</v>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="154">
@@ -8758,8 +9062,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N154" t="n">
-        <v>4</v>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="155">
@@ -8812,8 +9118,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N155" t="n">
-        <v>3</v>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="156">
@@ -8866,8 +9174,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N156" t="n">
-        <v>1</v>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="157">
@@ -8920,8 +9230,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N157" t="n">
-        <v>1</v>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="158">
@@ -8974,8 +9286,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N158" t="n">
-        <v>1</v>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -9028,8 +9342,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N159" t="n">
-        <v>2</v>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="160">
@@ -9082,8 +9398,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N160" t="n">
-        <v>0</v>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -9136,8 +9454,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N161" t="n">
-        <v>0</v>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="162">
@@ -9190,8 +9510,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N162" t="n">
-        <v>4</v>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="163">
@@ -9244,8 +9566,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N163" t="n">
-        <v>0</v>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="164">
@@ -9298,8 +9622,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N164" t="n">
-        <v>0</v>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="165">
@@ -9352,8 +9678,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N165" t="n">
-        <v>0</v>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="166">
@@ -9406,8 +9734,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N166" t="n">
-        <v>0</v>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="167">
@@ -9460,8 +9790,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N167" t="n">
-        <v>0</v>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="168">
@@ -9514,8 +9846,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N168" t="n">
-        <v>1</v>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -9568,8 +9902,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N169" t="n">
-        <v>0</v>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="170">
@@ -9622,8 +9958,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N170" t="n">
-        <v>3</v>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -9676,8 +10014,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N171" t="n">
-        <v>0</v>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="172">
@@ -9730,8 +10070,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N172" t="n">
-        <v>1</v>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="173">
@@ -9784,8 +10126,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N173" t="n">
-        <v>0</v>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="174">
@@ -9838,8 +10182,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N174" t="n">
-        <v>4</v>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="175">
@@ -9892,8 +10238,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N175" t="n">
-        <v>1</v>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="176">
@@ -9946,8 +10294,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N176" t="n">
-        <v>0</v>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="177">
@@ -10000,8 +10350,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N177" t="n">
-        <v>1</v>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="178">
@@ -10054,8 +10406,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N178" t="n">
-        <v>0</v>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -10108,8 +10462,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N179" t="n">
-        <v>0</v>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="180">
@@ -10162,8 +10518,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N180" t="n">
-        <v>3</v>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -10216,8 +10574,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N181" t="n">
-        <v>2</v>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="182">
@@ -10270,8 +10630,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N182" t="n">
-        <v>0</v>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="183">
@@ -10324,8 +10686,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N183" t="n">
-        <v>0</v>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="184">
@@ -10378,8 +10742,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N184" t="n">
-        <v>1</v>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="185">
@@ -10432,8 +10798,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N185" t="n">
-        <v>0</v>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -10486,8 +10854,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N186" t="n">
-        <v>0</v>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="187">
@@ -10540,8 +10910,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N187" t="n">
-        <v>2</v>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="188">
@@ -10594,8 +10966,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N188" t="n">
-        <v>1</v>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -10648,8 +11022,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N189" t="n">
-        <v>2</v>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="190">
@@ -10702,8 +11078,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N190" t="n">
-        <v>0</v>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -10756,8 +11134,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N191" t="n">
-        <v>3</v>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="192">
@@ -10810,8 +11190,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N192" t="n">
-        <v>2</v>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="193">
@@ -10864,8 +11246,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N193" t="n">
-        <v>0</v>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="194">
@@ -10918,8 +11302,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N194" t="n">
-        <v>3</v>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="195">
@@ -10972,8 +11358,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N195" t="n">
-        <v>0</v>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="196">
@@ -11026,8 +11414,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N196" t="n">
-        <v>0</v>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="197">
@@ -11080,8 +11470,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N197" t="n">
-        <v>0</v>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="198">
@@ -11134,8 +11526,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N198" t="n">
-        <v>1</v>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -11188,8 +11582,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N199" t="n">
-        <v>0</v>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="200">
@@ -11242,8 +11638,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N200" t="n">
-        <v>0</v>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -11296,8 +11694,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N201" t="n">
-        <v>0</v>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="202">
@@ -11350,8 +11750,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N202" t="n">
-        <v>0</v>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="203">
@@ -11404,8 +11806,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N203" t="n">
-        <v>0</v>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="204">
@@ -11458,8 +11862,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N204" t="n">
-        <v>3</v>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="205">
@@ -11512,8 +11918,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N205" t="n">
-        <v>3</v>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="206">
@@ -11566,8 +11974,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N206" t="n">
-        <v>3</v>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="207">
@@ -11620,8 +12030,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N207" t="n">
-        <v>0</v>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -11674,8 +12086,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N208" t="n">
-        <v>1</v>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="209">
@@ -11728,8 +12142,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N209" t="n">
-        <v>0</v>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -11782,8 +12198,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N210" t="n">
-        <v>4</v>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="211">
@@ -11836,8 +12254,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N211" t="n">
-        <v>0</v>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="212">
@@ -11890,8 +12310,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N212" t="n">
-        <v>3</v>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="213">
@@ -11944,8 +12366,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N213" t="n">
-        <v>1</v>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="214">
@@ -11998,8 +12422,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N214" t="n">
-        <v>0</v>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="215">
@@ -12052,8 +12478,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N215" t="n">
-        <v>0</v>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="216">
@@ -12106,8 +12534,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N216" t="n">
-        <v>0</v>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="217">
@@ -12160,8 +12590,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N217" t="n">
-        <v>0</v>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -12214,8 +12646,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N218" t="n">
-        <v>0</v>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="219">
@@ -12268,8 +12702,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N219" t="n">
-        <v>0</v>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="220">
@@ -12322,8 +12758,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N220" t="n">
-        <v>0</v>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="221">
@@ -12376,8 +12814,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N221" t="n">
-        <v>0</v>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="222">
@@ -12430,8 +12870,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N222" t="n">
-        <v>3</v>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="223">
@@ -12484,8 +12926,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N223" t="n">
-        <v>1</v>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="224">
@@ -12538,8 +12982,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N224" t="n">
-        <v>0</v>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="225">
@@ -12592,8 +13038,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N225" t="n">
-        <v>0</v>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="226">
@@ -12646,8 +13094,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N226" t="n">
-        <v>0</v>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="227">
@@ -12700,8 +13150,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N227" t="n">
-        <v>3</v>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="228">
@@ -12754,8 +13206,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N228" t="n">
-        <v>2</v>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="229">
@@ -12808,8 +13262,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N229" t="n">
-        <v>0</v>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="230">
@@ -12862,8 +13318,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N230" t="n">
-        <v>2</v>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="231">
@@ -12916,8 +13374,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N231" t="n">
-        <v>1</v>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="232">
@@ -12970,8 +13430,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N232" t="n">
-        <v>0</v>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="233">
@@ -13024,8 +13486,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N233" t="n">
-        <v>0</v>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="234">
@@ -13078,8 +13542,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N234" t="n">
-        <v>3</v>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="235">
@@ -13132,8 +13598,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N235" t="n">
-        <v>2</v>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="236">
@@ -13186,8 +13654,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N236" t="n">
-        <v>1</v>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="237">
@@ -13240,8 +13710,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N237" t="n">
-        <v>0</v>
+      <c r="N237" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="238">
@@ -13294,8 +13766,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N238" t="n">
-        <v>0</v>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="239">
@@ -13348,8 +13822,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N239" t="n">
-        <v>0</v>
+      <c r="N239" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="240">
@@ -13402,8 +13878,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N240" t="n">
-        <v>0</v>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="241">
@@ -13456,8 +13934,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N241" t="n">
-        <v>0</v>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="242">
@@ -13510,8 +13990,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N242" t="n">
-        <v>2</v>
+      <c r="N242" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="243">
@@ -13564,8 +14046,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N243" t="n">
-        <v>0</v>
+      <c r="N243" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="244">
@@ -13618,8 +14102,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N244" t="n">
-        <v>2</v>
+      <c r="N244" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="245">
@@ -13672,8 +14158,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N245" t="n">
-        <v>2</v>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="246">
@@ -13726,8 +14214,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N246" t="n">
-        <v>1</v>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="247">
@@ -13780,8 +14270,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N247" t="n">
-        <v>3</v>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="248">
@@ -13834,8 +14326,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N248" t="n">
-        <v>0</v>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="249">
@@ -13888,8 +14382,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N249" t="n">
-        <v>0</v>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="250">
@@ -13942,8 +14438,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N250" t="n">
-        <v>1</v>
+      <c r="N250" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="251">
@@ -13996,8 +14494,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N251" t="n">
-        <v>0</v>
+      <c r="N251" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="252">
@@ -14050,8 +14550,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N252" t="n">
-        <v>0</v>
+      <c r="N252" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="253">
@@ -14104,8 +14606,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N253" t="n">
-        <v>0</v>
+      <c r="N253" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="254">
@@ -14158,8 +14662,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N254" t="n">
-        <v>0</v>
+      <c r="N254" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="255">
@@ -14212,8 +14718,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N255" t="n">
-        <v>0</v>
+      <c r="N255" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="256">
@@ -14266,8 +14774,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N256" t="n">
-        <v>0</v>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="257">
@@ -14320,8 +14830,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N257" t="n">
-        <v>0</v>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="258">
@@ -14374,8 +14886,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N258" t="n">
-        <v>1</v>
+      <c r="N258" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="259">
@@ -14428,8 +14942,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N259" t="n">
-        <v>0</v>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="260">
@@ -14482,8 +14998,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N260" t="n">
-        <v>3</v>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="261">
@@ -14536,8 +15054,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N261" t="n">
-        <v>0</v>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="262">
@@ -14590,8 +15110,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N262" t="n">
-        <v>0</v>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="263">
@@ -14644,8 +15166,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N263" t="n">
-        <v>4</v>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="264">
@@ -14698,8 +15222,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N264" t="n">
-        <v>2</v>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="265">
@@ -14752,8 +15278,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N265" t="n">
-        <v>2</v>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="266">
@@ -14806,8 +15334,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N266" t="n">
-        <v>1</v>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="267">
@@ -14860,8 +15390,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N267" t="n">
-        <v>0</v>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="268">
@@ -14914,8 +15446,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N268" t="n">
-        <v>1</v>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="269">
@@ -14968,8 +15502,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N269" t="n">
-        <v>0</v>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="270">
@@ -15022,8 +15558,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N270" t="n">
-        <v>2</v>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="271">
@@ -15076,8 +15614,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N271" t="n">
-        <v>0</v>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="272">
@@ -15130,8 +15670,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N272" t="n">
-        <v>1</v>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="273">
@@ -15184,8 +15726,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N273" t="n">
-        <v>0</v>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="274">
@@ -15238,8 +15782,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N274" t="n">
-        <v>0</v>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="275">
@@ -15292,8 +15838,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N275" t="n">
-        <v>0</v>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="276">
@@ -15346,8 +15894,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N276" t="n">
-        <v>1</v>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="277">
@@ -15400,8 +15950,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N277" t="n">
-        <v>0</v>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="278">
@@ -15454,8 +16006,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N278" t="n">
-        <v>2</v>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="279">
@@ -15508,8 +16062,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N279" t="n">
-        <v>0</v>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="280">
@@ -15562,8 +16118,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N280" t="n">
-        <v>3</v>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="281">
@@ -15616,8 +16174,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N281" t="n">
-        <v>0</v>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="282">
@@ -15670,8 +16230,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N282" t="n">
-        <v>2</v>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="283">
@@ -15724,8 +16286,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N283" t="n">
-        <v>4</v>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="284">
@@ -15778,8 +16342,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N284" t="n">
-        <v>2</v>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="285">
@@ -15832,8 +16398,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N285" t="n">
-        <v>0</v>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="286">
@@ -15886,8 +16454,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N286" t="n">
-        <v>0</v>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="287">
@@ -15940,8 +16510,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N287" t="n">
-        <v>1</v>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="288">
@@ -15994,8 +16566,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N288" t="n">
-        <v>0</v>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="289">
@@ -16048,8 +16622,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N289" t="n">
-        <v>2</v>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="290">
@@ -16102,8 +16678,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N290" t="n">
-        <v>2</v>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="291">
@@ -16156,8 +16734,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N291" t="n">
-        <v>1</v>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="292">
@@ -16210,8 +16790,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N292" t="n">
-        <v>0</v>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
       </c>
     </row>
     <row r="293">
@@ -16264,8 +16846,10 @@
           <t>fixed defect</t>
         </is>
       </c>
-      <c r="N293" t="n">
-        <v>3</v>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="294">
@@ -16318,8 +16902,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N294" t="n">
-        <v>1</v>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="295">
@@ -16372,8 +16958,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N295" t="n">
-        <v>1</v>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="296">
@@ -16426,8 +17014,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N296" t="n">
-        <v>2</v>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="297">
@@ -16480,8 +17070,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N297" t="n">
-        <v>3</v>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="298">
@@ -16534,8 +17126,10 @@
           <t>normal</t>
         </is>
       </c>
-      <c r="N298" t="n">
-        <v>1</v>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="299">
@@ -16588,8 +17182,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N299" t="n">
-        <v>1</v>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
     <row r="300">
@@ -16642,8 +17238,10 @@
           <t>reversable defect</t>
         </is>
       </c>
-      <c r="N300" t="n">
-        <v>1</v>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>Very Severe</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/data/heart_disease_clean.xlsx
+++ b/data/heart_disease_clean.xlsx
@@ -608,7 +608,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1448,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3464,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -3912,7 +3912,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -4136,7 +4136,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -4416,7 +4416,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -4696,7 +4696,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -4976,7 +4976,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7216,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -8224,7 +8224,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -8392,7 +8392,7 @@
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="N146" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -9120,7 +9120,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="N157" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="N158" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
       </c>
       <c r="N159" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="N168" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="N170" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
       </c>
       <c r="N172" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -10240,7 +10240,7 @@
       </c>
       <c r="N175" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="N177" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -10520,7 +10520,7 @@
       </c>
       <c r="N180" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -10576,7 +10576,7 @@
       </c>
       <c r="N181" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10744,7 @@
       </c>
       <c r="N184" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -10912,7 +10912,7 @@
       </c>
       <c r="N187" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -10968,7 +10968,7 @@
       </c>
       <c r="N188" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -11024,7 +11024,7 @@
       </c>
       <c r="N189" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -11136,7 +11136,7 @@
       </c>
       <c r="N191" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="N192" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -11528,7 +11528,7 @@
       </c>
       <c r="N198" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -11920,7 +11920,7 @@
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -11976,7 +11976,7 @@
       </c>
       <c r="N206" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -12088,7 +12088,7 @@
       </c>
       <c r="N208" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="N212" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -12368,7 +12368,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -12872,7 +12872,7 @@
       </c>
       <c r="N222" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -12928,7 +12928,7 @@
       </c>
       <c r="N223" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -13152,7 +13152,7 @@
       </c>
       <c r="N227" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="N228" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="N230" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -13376,7 +13376,7 @@
       </c>
       <c r="N231" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -13544,7 +13544,7 @@
       </c>
       <c r="N234" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -13600,7 +13600,7 @@
       </c>
       <c r="N235" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -13656,7 +13656,7 @@
       </c>
       <c r="N236" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -13992,7 +13992,7 @@
       </c>
       <c r="N242" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -14104,7 +14104,7 @@
       </c>
       <c r="N244" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -14160,7 +14160,7 @@
       </c>
       <c r="N245" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -14216,7 +14216,7 @@
       </c>
       <c r="N246" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -14272,7 +14272,7 @@
       </c>
       <c r="N247" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14440,7 @@
       </c>
       <c r="N250" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="N258" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -15000,7 +15000,7 @@
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -15280,7 +15280,7 @@
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -15448,7 +15448,7 @@
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -15560,7 +15560,7 @@
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -15672,7 +15672,7 @@
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -15896,7 +15896,7 @@
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -16120,7 +16120,7 @@
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -16232,7 +16232,7 @@
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="N284" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -16624,7 +16624,7 @@
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -16680,7 +16680,7 @@
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -16736,7 +16736,7 @@
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -16904,7 +16904,7 @@
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -16960,7 +16960,7 @@
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -17016,7 +17016,7 @@
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Moderate</t>
         </is>
       </c>
     </row>
@@ -17072,7 +17072,7 @@
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Severe</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="N298" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -17184,7 +17184,7 @@
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
@@ -17240,7 +17240,7 @@
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>Very Severe</t>
+          <t>Mild</t>
         </is>
       </c>
     </row>
